--- a/My Job/Template_LAPORAN KEGIATAN.xlsx
+++ b/My Job/Template_LAPORAN KEGIATAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Smart Volunteers PMI Kota Cilegon\My Job\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC56A9CB-24CD-48C6-829C-B3F77EB5C138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA68B23-B79A-4D4A-964F-953F175840F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
